--- a/produkte+.xlsx
+++ b/produkte+.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\app_iphone_shitjet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC0B111-B9C9-4857-A998-F386E7D8F252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA34E144-C4E7-4FF5-9639-E3DC3423F157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F852DC8A-6273-46A5-80EE-4F7A2FD95859}"/>
   </bookViews>
@@ -5454,7 +5454,14 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Per cent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -32659,25 +32666,25 @@
     <mergeCell ref="E5:E6"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7:H1013">
-    <cfRule type="expression" dxfId="6" priority="4">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>$E7="AKTIV"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:E1013">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
       <formula>"AKTIV"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H4">
-    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",H3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -32738,7 +32745,7 @@
         <v>4.4849999999999994</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>30</v>
@@ -32764,7 +32771,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>30</v>
@@ -32790,7 +32797,7 @@
         <v>2.33</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>30</v>
@@ -32816,7 +32823,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>30</v>
@@ -32842,7 +32849,7 @@
         <v>3.6</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>30</v>
@@ -32868,7 +32875,7 @@
         <v>3.2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>30</v>
@@ -32894,7 +32901,7 @@
         <v>3.5</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>63</v>
@@ -32920,7 +32927,7 @@
         <v>1.93</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>30</v>
@@ -32946,7 +32953,7 @@
         <v>1.9649999999999999</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>30</v>
@@ -32972,7 +32979,7 @@
         <v>2.8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>30</v>
@@ -32998,7 +33005,7 @@
         <v>2.7650000000000001</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>30</v>
@@ -33024,7 +33031,7 @@
         <v>5.3</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>30</v>
@@ -33050,7 +33057,7 @@
         <v>1.7</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>30</v>
@@ -33076,7 +33083,7 @@
         <v>1.62</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>30</v>
@@ -33102,7 +33109,7 @@
         <v>0.18</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>30</v>
@@ -33128,7 +33135,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>63</v>
@@ -33154,7 +33161,7 @@
         <v>1.5</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>30</v>
@@ -33180,7 +33187,7 @@
         <v>1.5</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>30</v>
@@ -33206,7 +33213,7 @@
         <v>1.5</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>30</v>
@@ -33232,7 +33239,7 @@
         <v>3</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>30</v>
@@ -33258,7 +33265,7 @@
         <v>3</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>30</v>
@@ -33284,7 +33291,7 @@
         <v>3</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>63</v>
@@ -33310,7 +33317,7 @@
         <v>6</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>30</v>
@@ -33336,7 +33343,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>30</v>
@@ -33362,7 +33369,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>30</v>
@@ -33388,7 +33395,7 @@
         <v>3</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>63</v>
@@ -33414,7 +33421,7 @@
         <v>3</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>63</v>
@@ -33440,7 +33447,7 @@
         <v>3</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>63</v>
@@ -33466,7 +33473,7 @@
         <v>6</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>63</v>
@@ -33492,7 +33499,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>30</v>
@@ -33518,7 +33525,7 @@
         <v>7.15</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>30</v>
@@ -33544,7 +33551,7 @@
         <v>2</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>63</v>
@@ -33570,7 +33577,7 @@
         <v>2</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>63</v>
@@ -33596,7 +33603,7 @@
         <v>2</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>63</v>
@@ -33622,7 +33629,7 @@
         <v>3</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>63</v>
@@ -33648,7 +33655,7 @@
         <v>3</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>63</v>
@@ -33674,7 +33681,7 @@
         <v>3</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>63</v>
@@ -33700,7 +33707,7 @@
         <v>4</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>63</v>
@@ -33726,7 +33733,7 @@
         <v>4</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>63</v>
@@ -33752,7 +33759,7 @@
         <v>0.70399999999999996</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>63</v>
@@ -33778,7 +33785,7 @@
         <v>0.7</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1216</v>
+        <v>115</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>30</v>
@@ -33804,7 +33811,7 @@
         <v>0.6</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>1216</v>
+        <v>115</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>63</v>
@@ -33830,7 +33837,7 @@
         <v>0.6</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1216</v>
+        <v>115</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>63</v>
@@ -33856,7 +33863,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1216</v>
+        <v>115</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>63</v>
@@ -33882,7 +33889,7 @@
         <v>1.8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>63</v>
@@ -33908,7 +33915,7 @@
         <v>1.8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>63</v>
@@ -33934,7 +33941,7 @@
         <v>1.8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>63</v>
@@ -33960,7 +33967,7 @@
         <v>1.32</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>63</v>
@@ -33986,7 +33993,7 @@
         <v>1.32</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>63</v>
@@ -34012,7 +34019,7 @@
         <v>1.32</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>63</v>
@@ -34038,7 +34045,7 @@
         <v>5</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>63</v>
@@ -34064,7 +34071,7 @@
         <v>5</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>63</v>
@@ -34090,7 +34097,7 @@
         <v>0.33</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>30</v>
@@ -34116,7 +34123,7 @@
         <v>5</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>30</v>
@@ -34142,7 +34149,7 @@
         <v>1.8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>1218</v>
+        <v>145</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>63</v>
@@ -34168,7 +34175,7 @@
         <v>1.8</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>1218</v>
+        <v>145</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>63</v>
@@ -34194,7 +34201,7 @@
         <v>1.32</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>1218</v>
+        <v>145</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>63</v>
@@ -34220,7 +34227,7 @@
         <v>1.8</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>1218</v>
+        <v>145</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>30</v>
@@ -34246,7 +34253,7 @@
         <v>1</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>30</v>
@@ -34272,7 +34279,7 @@
         <v>1.5</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>30</v>
@@ -34298,7 +34305,7 @@
         <v>1.84</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>63</v>
@@ -34324,7 +34331,7 @@
         <v>0.33</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>30</v>
@@ -34350,7 +34357,7 @@
         <v>5</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>30</v>
@@ -34376,7 +34383,7 @@
         <v>5</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>30</v>
@@ -34402,7 +34409,7 @@
         <v>1</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>30</v>
@@ -34428,7 +34435,7 @@
         <v>1.5</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>30</v>
@@ -34454,7 +34461,7 @@
         <v>2</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>63</v>
@@ -34480,7 +34487,7 @@
         <v>0.33</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>30</v>
@@ -34506,7 +34513,7 @@
         <v>1</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>30</v>
@@ -34532,7 +34539,7 @@
         <v>1.5</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>30</v>
@@ -34558,7 +34565,7 @@
         <v>2</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>30</v>
@@ -34584,7 +34591,7 @@
         <v>1</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>30</v>
@@ -34610,7 +34617,7 @@
         <v>2</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>30</v>
@@ -34636,7 +34643,7 @@
         <v>1</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>30</v>
@@ -34662,7 +34669,7 @@
         <v>2</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>30</v>
@@ -34688,7 +34695,7 @@
         <v>1</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>30</v>
@@ -34714,7 +34721,7 @@
         <v>2</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>30</v>
@@ -34740,7 +34747,7 @@
         <v>1</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>1219</v>
+        <v>193</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>63</v>
@@ -34766,7 +34773,7 @@
         <v>1</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>1219</v>
+        <v>193</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>63</v>
@@ -34792,7 +34799,7 @@
         <v>1</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>1219</v>
+        <v>193</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>63</v>
@@ -34818,7 +34825,7 @@
         <v>2.5</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>1219</v>
+        <v>193</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>63</v>
@@ -34844,7 +34851,7 @@
         <v>2.5</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>1219</v>
+        <v>193</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>63</v>
@@ -34870,7 +34877,7 @@
         <v>5</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>1219</v>
+        <v>193</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>63</v>
@@ -34896,7 +34903,7 @@
         <v>5</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>1219</v>
+        <v>193</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>63</v>
@@ -34922,7 +34929,7 @@
         <v>1</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>30</v>
@@ -34948,7 +34955,7 @@
         <v>0.48499999999999999</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>30</v>
@@ -34974,7 +34981,7 @@
         <v>0.48499999999999999</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>30</v>
@@ -35000,7 +35007,7 @@
         <v>0.48499999999999999</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>30</v>
@@ -35026,7 +35033,7 @@
         <v>0.48499999999999999</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>30</v>
@@ -35052,7 +35059,7 @@
         <v>0.48499999999999999</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>30</v>
@@ -35078,7 +35085,7 @@
         <v>0.48499999999999999</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>30</v>
@@ -35104,7 +35111,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>30</v>
@@ -35130,7 +35137,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>30</v>
@@ -35156,7 +35163,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>30</v>
@@ -35182,7 +35189,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>30</v>
@@ -35208,7 +35215,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>30</v>
@@ -35234,7 +35241,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>30</v>
@@ -35260,7 +35267,7 @@
         <v>0.48</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>63</v>
@@ -35286,7 +35293,7 @@
         <v>0.78</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>63</v>
@@ -35312,7 +35319,7 @@
         <v>1.46</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>30</v>
@@ -35338,7 +35345,7 @@
         <v>1.46</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>30</v>
@@ -35364,7 +35371,7 @@
         <v>2</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>1221</v>
+        <v>243</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>63</v>
@@ -35390,7 +35397,7 @@
         <v>2</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>1221</v>
+        <v>243</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>63</v>
@@ -35416,7 +35423,7 @@
         <v>5</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>63</v>
@@ -35442,7 +35449,7 @@
         <v>2.65</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>63</v>
@@ -35468,7 +35475,7 @@
         <v>2.65</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>63</v>
@@ -35494,7 +35501,7 @@
         <v>2.65</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>63</v>
@@ -35520,7 +35527,7 @@
         <v>2.65</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>1226</v>
+        <v>256</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>30</v>
@@ -35546,7 +35553,7 @@
         <v>2.65</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>1226</v>
+        <v>256</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>30</v>
@@ -35572,7 +35579,7 @@
         <v>0.7</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>1225</v>
+        <v>261</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>63</v>
@@ -35598,7 +35605,7 @@
         <v>1</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>1225</v>
+        <v>261</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>30</v>
@@ -35624,7 +35631,7 @@
         <v>6</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>1225</v>
+        <v>261</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>30</v>
@@ -35728,7 +35735,7 @@
         <v>1</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>63</v>
@@ -35754,7 +35761,7 @@
         <v>1</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>63</v>
@@ -35780,7 +35787,7 @@
         <v>1</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>63</v>
@@ -35806,7 +35813,7 @@
         <v>1</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>30</v>
@@ -35832,7 +35839,7 @@
         <v>1</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>63</v>
@@ -35858,7 +35865,7 @@
         <v>1</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>63</v>
@@ -35884,7 +35891,7 @@
         <v>1</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>30</v>
@@ -35910,7 +35917,7 @@
         <v>1</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>30</v>
@@ -35936,7 +35943,7 @@
         <v>2.65</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>63</v>
@@ -35962,7 +35969,7 @@
         <v>2.65</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>63</v>
@@ -35988,7 +35995,7 @@
         <v>2.65</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>63</v>
@@ -36014,7 +36021,7 @@
         <v>0</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>30</v>
@@ -36040,7 +36047,7 @@
         <v>5</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>30</v>
@@ -36066,7 +36073,7 @@
         <v>5</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>30</v>
@@ -36092,7 +36099,7 @@
         <v>5</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>1226</v>
+        <v>256</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>63</v>
@@ -36118,7 +36125,7 @@
         <v>1</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>1226</v>
+        <v>256</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>30</v>
@@ -36144,7 +36151,7 @@
         <v>1</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>30</v>
@@ -36170,7 +36177,7 @@
         <v>1</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>1228</v>
+        <v>310</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>30</v>
@@ -36196,7 +36203,7 @@
         <v>5</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>1228</v>
+        <v>310</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>30</v>
@@ -36248,7 +36255,7 @@
         <v>0.4</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>1223</v>
+        <v>317</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>30</v>
@@ -36274,7 +36281,7 @@
         <v>0.3</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>1223</v>
+        <v>317</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>30</v>
@@ -36300,7 +36307,7 @@
         <v>0.25</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>1223</v>
+        <v>317</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>63</v>
@@ -36326,7 +36333,7 @@
         <v>1</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>1223</v>
+        <v>317</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>30</v>
@@ -36456,7 +36463,7 @@
         <v>0.75</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>30</v>
@@ -36482,7 +36489,7 @@
         <v>1</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>30</v>
@@ -36508,7 +36515,7 @@
         <v>1</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>30</v>
@@ -36560,7 +36567,7 @@
         <v>0.5</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>30</v>
@@ -36586,7 +36593,7 @@
         <v>1.45</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>30</v>
@@ -36612,7 +36619,7 @@
         <v>3</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>30</v>
@@ -36638,7 +36645,7 @@
         <v>4.32</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>30</v>
@@ -36664,7 +36671,7 @@
         <v>3.32</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>30</v>
@@ -36690,7 +36697,7 @@
         <v>3.8</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>30</v>
@@ -36716,7 +36723,7 @@
         <v>3.5</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>30</v>
@@ -36742,7 +36749,7 @@
         <v>7.9499999999999993</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>30</v>
@@ -36768,7 +36775,7 @@
         <v>4</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>30</v>
@@ -36794,7 +36801,7 @@
         <v>2.64</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>30</v>
@@ -36820,7 +36827,7 @@
         <v>3.6</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>30</v>
@@ -36846,7 +36853,7 @@
         <v>2.84</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>30</v>
@@ -36872,7 +36879,7 @@
         <v>2.8050000000000002</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>30</v>
@@ -36898,7 +36905,7 @@
         <v>3.32</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>30</v>
@@ -36924,7 +36931,7 @@
         <v>6</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>30</v>
@@ -36950,7 +36957,7 @@
         <v>3.12</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>30</v>
@@ -36976,7 +36983,7 @@
         <v>3</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>30</v>
@@ -37002,7 +37009,7 @@
         <v>3</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>63</v>
@@ -37028,7 +37035,7 @@
         <v>1</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>1219</v>
+        <v>193</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>63</v>
@@ -37054,7 +37061,7 @@
         <v>1</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>1219</v>
+        <v>193</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>63</v>
@@ -37080,7 +37087,7 @@
         <v>2.5</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>1219</v>
+        <v>193</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>63</v>
@@ -37106,7 +37113,7 @@
         <v>2.5</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>1219</v>
+        <v>193</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>63</v>
@@ -37132,7 +37139,7 @@
         <v>0.75</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>1227</v>
+        <v>386</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>30</v>
@@ -37158,7 +37165,7 @@
         <v>3</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>30</v>
@@ -37184,7 +37191,7 @@
         <v>3</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>30</v>
@@ -37210,7 +37217,7 @@
         <v>3</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>30</v>
@@ -37236,7 +37243,7 @@
         <v>3</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>30</v>
@@ -37262,7 +37269,7 @@
         <v>3</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>30</v>
@@ -37288,7 +37295,7 @@
         <v>3</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>30</v>
@@ -37314,7 +37321,7 @@
         <v>0.75</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>30</v>
@@ -37340,7 +37347,7 @@
         <v>2</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>30</v>
@@ -37366,7 +37373,7 @@
         <v>2</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>30</v>
@@ -37392,7 +37399,7 @@
         <v>5</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>63</v>
@@ -37418,7 +37425,7 @@
         <v>0.7</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>1216</v>
+        <v>115</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>30</v>
@@ -37444,7 +37451,7 @@
         <v>2</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>30</v>
@@ -37470,7 +37477,7 @@
         <v>0.5</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>30</v>
@@ -37496,7 +37503,7 @@
         <v>0.5</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>30</v>
@@ -37522,7 +37529,7 @@
         <v>0.5</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>30</v>
@@ -37548,7 +37555,7 @@
         <v>0.5</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>30</v>
@@ -37574,7 +37581,7 @@
         <v>0.75</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>30</v>
@@ -37600,7 +37607,7 @@
         <v>0.75</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>30</v>
@@ -37626,7 +37633,7 @@
         <v>0.75</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>30</v>
@@ -37652,7 +37659,7 @@
         <v>3</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>30</v>
@@ -37678,7 +37685,7 @@
         <v>1</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>30</v>
@@ -37704,7 +37711,7 @@
         <v>1</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>30</v>
@@ -37730,7 +37737,7 @@
         <v>1</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>30</v>
@@ -37756,7 +37763,7 @@
         <v>1</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>30</v>
@@ -37782,7 +37789,7 @@
         <v>5</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>30</v>
@@ -37808,7 +37815,7 @@
         <v>3</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>30</v>
@@ -37834,7 +37841,7 @@
         <v>0.75</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>30</v>
@@ -37860,7 +37867,7 @@
         <v>0.75</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>30</v>
@@ -37886,7 +37893,7 @@
         <v>0.5</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>30</v>
@@ -37912,7 +37919,7 @@
         <v>0.5</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>30</v>
@@ -37938,7 +37945,7 @@
         <v>1</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>30</v>
@@ -37964,7 +37971,7 @@
         <v>1</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>1219</v>
+        <v>193</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>30</v>
@@ -37990,7 +37997,7 @@
         <v>0.33</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>30</v>
@@ -38016,7 +38023,7 @@
         <v>0.33</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>30</v>
@@ -38042,7 +38049,7 @@
         <v>0.33</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>30</v>
@@ -38172,7 +38179,7 @@
         <v>6.7889999999999997</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>63</v>
@@ -38198,7 +38205,7 @@
         <v>4.5670000000000002</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>63</v>
@@ -38224,7 +38231,7 @@
         <v>3.456</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>63</v>
@@ -38250,7 +38257,7 @@
         <v>0.92</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>63</v>
@@ -38276,7 +38283,7 @@
         <v>0.92</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>63</v>
@@ -38302,7 +38309,7 @@
         <v>1.84</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>63</v>
@@ -38328,7 +38335,7 @@
         <v>1.84</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>63</v>
@@ -38354,7 +38361,7 @@
         <v>0.6</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>1216</v>
+        <v>115</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>63</v>
@@ -38380,7 +38387,7 @@
         <v>1.84</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>63</v>
@@ -38406,7 +38413,7 @@
         <v>1.84</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>63</v>
@@ -38432,7 +38439,7 @@
         <v>0.92</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>63</v>
@@ -38458,7 +38465,7 @@
         <v>0.92</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>63</v>
@@ -38484,7 +38491,7 @@
         <v>5</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>63</v>
@@ -38536,7 +38543,7 @@
         <v>1.8</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>30</v>
@@ -38588,7 +38595,7 @@
         <v>2.64</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>30</v>
@@ -38614,7 +38621,7 @@
         <v>3.48</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>30</v>
@@ -38640,7 +38647,7 @@
         <v>5.9670000000000005</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>63</v>
@@ -38666,7 +38673,7 @@
         <v>5.2560000000000002</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>30</v>
@@ -38692,7 +38699,7 @@
         <v>5.8870000000000005</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>30</v>
@@ -38744,7 +38751,7 @@
         <v>2.64</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>30</v>
@@ -38770,7 +38777,7 @@
         <v>2.64</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>30</v>
@@ -38796,7 +38803,7 @@
         <v>2.64</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>30</v>
@@ -38822,7 +38829,7 @@
         <v>1.4</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>30</v>
@@ -38874,7 +38881,7 @@
         <v>5</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>30</v>
@@ -38900,7 +38907,7 @@
         <v>2</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>30</v>
@@ -38926,7 +38933,7 @@
         <v>3</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>30</v>
@@ -38952,7 +38959,7 @@
         <v>2.72</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>30</v>
@@ -38978,7 +38985,7 @@
         <v>3.6</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>30</v>
@@ -39004,7 +39011,7 @@
         <v>5</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>30</v>
@@ -39030,7 +39037,7 @@
         <v>4.8</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>30</v>
@@ -39056,7 +39063,7 @@
         <v>5.3</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>30</v>
@@ -39082,7 +39089,7 @@
         <v>5.84</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>30</v>
@@ -39108,7 +39115,7 @@
         <v>2.3200000000000003</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>30</v>
@@ -39134,7 +39141,7 @@
         <v>4.5</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>30</v>
@@ -39160,7 +39167,7 @@
         <v>4.9649999999999999</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>30</v>
@@ -39186,7 +39193,7 @@
         <v>2.8</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>30</v>
@@ -39212,7 +39219,7 @@
         <v>4.32</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>30</v>
@@ -39238,7 +39245,7 @@
         <v>4</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>30</v>
@@ -39264,7 +39271,7 @@
         <v>3.12</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>30</v>
@@ -39290,7 +39297,7 @@
         <v>3.12</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>30</v>
@@ -39316,7 +39323,7 @@
         <v>5.8</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>30</v>
@@ -39342,7 +39349,7 @@
         <v>5</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>63</v>
@@ -39368,7 +39375,7 @@
         <v>2.1</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E257" s="2" t="s">
         <v>30</v>
@@ -39394,7 +39401,7 @@
         <v>2.92</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>30</v>
@@ -39420,7 +39427,7 @@
         <v>3</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E259" s="2" t="s">
         <v>30</v>
@@ -39446,7 +39453,7 @@
         <v>2.1</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>30</v>
@@ -39472,7 +39479,7 @@
         <v>3.3200000000000003</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E261" s="2" t="s">
         <v>30</v>
@@ -39498,7 +39505,7 @@
         <v>2.7800000000000002</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>30</v>
@@ -39524,7 +39531,7 @@
         <v>1.8</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E263" s="2" t="s">
         <v>30</v>
@@ -39550,7 +39557,7 @@
         <v>3.7800000000000002</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>63</v>
@@ -39576,7 +39583,7 @@
         <v>1.26</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>63</v>
@@ -39602,7 +39609,7 @@
         <v>2</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E266" s="2" t="s">
         <v>30</v>
@@ -39680,7 +39687,7 @@
         <v>1.8</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>30</v>
@@ -39706,7 +39713,7 @@
         <v>3.5</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E270" s="2" t="s">
         <v>30</v>
@@ -39732,7 +39739,7 @@
         <v>8.5890000000000004</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>30</v>
@@ -39758,7 +39765,7 @@
         <v>9.4290000000000003</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>30</v>
@@ -39862,7 +39869,7 @@
         <v>8.8889999999999993</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E276" s="2" t="s">
         <v>63</v>
@@ -39888,7 +39895,7 @@
         <v>3.48</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E277" s="2" t="s">
         <v>30</v>
@@ -39914,7 +39921,7 @@
         <v>2.48</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>30</v>
@@ -39940,7 +39947,7 @@
         <v>5.32</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>30</v>
@@ -40018,7 +40025,7 @@
         <v>1.23</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>30</v>
@@ -40044,7 +40051,7 @@
         <v>3.64</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>30</v>
@@ -40070,7 +40077,7 @@
         <v>4.3760000000000003</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>63</v>
@@ -40096,7 +40103,7 @@
         <v>4.7759999999999998</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E285" s="2" t="s">
         <v>63</v>
@@ -40122,7 +40129,7 @@
         <v>4.8559999999999999</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E286" s="2" t="s">
         <v>63</v>
@@ -40148,7 +40155,7 @@
         <v>2</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E287" s="2" t="s">
         <v>30</v>
@@ -40174,7 +40181,7 @@
         <v>2.8000000000000003</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>30</v>
@@ -40200,7 +40207,7 @@
         <v>3.12</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E289" s="2" t="s">
         <v>30</v>
@@ -40226,7 +40233,7 @@
         <v>0.96</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E290" s="2" t="s">
         <v>30</v>
@@ -40252,7 +40259,7 @@
         <v>2.64</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E291" s="2" t="s">
         <v>30</v>
@@ -40278,7 +40285,7 @@
         <v>5.2960000000000003</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E292" s="2" t="s">
         <v>30</v>
@@ -40304,7 +40311,7 @@
         <v>6.8070000000000004</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E293" s="2" t="s">
         <v>30</v>
@@ -40330,7 +40337,7 @@
         <v>9.9489999999999998</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E294" s="2" t="s">
         <v>63</v>
@@ -40356,7 +40363,7 @@
         <v>8.1869999999999994</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>63</v>
@@ -40382,7 +40389,7 @@
         <v>3.16</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E296" s="2" t="s">
         <v>30</v>
@@ -40408,7 +40415,7 @@
         <v>3.68</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E297" s="2" t="s">
         <v>63</v>
@@ -40434,7 +40441,7 @@
         <v>2.7839999999999998</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E298" s="2" t="s">
         <v>63</v>
@@ -40460,7 +40467,7 @@
         <v>2.8000000000000003</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E299" s="2" t="s">
         <v>30</v>
@@ -40486,7 +40493,7 @@
         <v>3.92</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>30</v>
@@ -40512,7 +40519,7 @@
         <v>4</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E301" s="2" t="s">
         <v>30</v>
@@ -40538,7 +40545,7 @@
         <v>3.64</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E302" s="2" t="s">
         <v>30</v>
@@ -40590,7 +40597,7 @@
         <v>2</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E304" s="2" t="s">
         <v>30</v>
@@ -40616,7 +40623,7 @@
         <v>2</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E305" s="2" t="s">
         <v>30</v>
@@ -40642,7 +40649,7 @@
         <v>2</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E306" s="2" t="s">
         <v>30</v>
@@ -40668,7 +40675,7 @@
         <v>3</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E307" s="2" t="s">
         <v>30</v>
@@ -40694,7 +40701,7 @@
         <v>1.8</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E308" s="2" t="s">
         <v>30</v>
@@ -40720,7 +40727,7 @@
         <v>7.407</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E309" s="2" t="s">
         <v>30</v>
@@ -40746,7 +40753,7 @@
         <v>7.569</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E310" s="2" t="s">
         <v>30</v>
@@ -40772,7 +40779,7 @@
         <v>8.8889999999999993</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E311" s="2" t="s">
         <v>30</v>
@@ -40798,7 +40805,7 @@
         <v>5.9670000000000005</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E312" s="2" t="s">
         <v>30</v>
@@ -40824,7 +40831,7 @@
         <v>5.1560000000000006</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E313" s="2" t="s">
         <v>63</v>
@@ -40850,7 +40857,7 @@
         <v>6.2670000000000003</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E314" s="2" t="s">
         <v>30</v>
@@ -40876,7 +40883,7 @@
         <v>5.556</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E315" s="2" t="s">
         <v>63</v>
@@ -40902,7 +40909,7 @@
         <v>2.085</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E316" s="2" t="s">
         <v>30</v>
@@ -40928,7 +40935,7 @@
         <v>2.8050000000000002</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E317" s="2" t="s">
         <v>30</v>
@@ -40954,7 +40961,7 @@
         <v>4</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E318" s="2" t="s">
         <v>30</v>
@@ -40980,7 +40987,7 @@
         <v>3</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E319" s="2" t="s">
         <v>30</v>
@@ -41006,7 +41013,7 @@
         <v>3.3</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E320" s="2" t="s">
         <v>30</v>
@@ -41032,7 +41039,7 @@
         <v>4.5</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E321" s="2" t="s">
         <v>30</v>
@@ -41058,7 +41065,7 @@
         <v>3</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E322" s="2" t="s">
         <v>30</v>
@@ -41084,7 +41091,7 @@
         <v>5</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E323" s="2" t="s">
         <v>30</v>
@@ -41110,7 +41117,7 @@
         <v>5</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E324" s="2" t="s">
         <v>30</v>
@@ -41136,7 +41143,7 @@
         <v>1.32</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E325" s="2" t="s">
         <v>30</v>
@@ -41162,7 +41169,7 @@
         <v>3.7800000000000002</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E326" s="2" t="s">
         <v>30</v>
@@ -41188,7 +41195,7 @@
         <v>5.8</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E327" s="2" t="s">
         <v>30</v>
@@ -41266,7 +41273,7 @@
         <v>3.12</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E330" s="2" t="s">
         <v>30</v>
@@ -41292,7 +41299,7 @@
         <v>1.8</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E331" s="2" t="s">
         <v>30</v>
@@ -41318,7 +41325,7 @@
         <v>2.64</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E332" s="2" t="s">
         <v>30</v>
@@ -41370,7 +41377,7 @@
         <v>4.5</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E334" s="2" t="s">
         <v>30</v>
@@ -41396,7 +41403,7 @@
         <v>1.8</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E335" s="2" t="s">
         <v>30</v>
@@ -41526,7 +41533,7 @@
         <v>7</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E340" s="2" t="s">
         <v>30</v>
@@ -41708,7 +41715,7 @@
         <v>1</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>1230</v>
+        <v>741</v>
       </c>
       <c r="E347" s="2" t="s">
         <v>63</v>
@@ -41734,7 +41741,7 @@
         <v>3</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>1230</v>
+        <v>741</v>
       </c>
       <c r="E348" s="2" t="s">
         <v>63</v>
@@ -41760,7 +41767,7 @@
         <v>4</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>1230</v>
+        <v>741</v>
       </c>
       <c r="E349" s="2" t="s">
         <v>63</v>
@@ -41786,7 +41793,7 @@
         <v>5</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>1230</v>
+        <v>741</v>
       </c>
       <c r="E350" s="2" t="s">
         <v>63</v>
@@ -41812,7 +41819,7 @@
         <v>0</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>1230</v>
+        <v>741</v>
       </c>
       <c r="E351" s="2" t="s">
         <v>30</v>
@@ -41838,7 +41845,7 @@
         <v>0</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>1230</v>
+        <v>741</v>
       </c>
       <c r="E352" s="2" t="s">
         <v>30</v>
@@ -45088,7 +45095,7 @@
         <v>3.96</v>
       </c>
       <c r="D477" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E477" s="2" t="s">
         <v>63</v>
@@ -45114,7 +45121,7 @@
         <v>1</v>
       </c>
       <c r="D478" s="2" t="s">
-        <v>1230</v>
+        <v>741</v>
       </c>
       <c r="E478" s="2" t="s">
         <v>63</v>
@@ -45140,7 +45147,7 @@
         <v>1.8</v>
       </c>
       <c r="D479" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E479" s="2" t="s">
         <v>63</v>
@@ -45166,7 +45173,7 @@
         <v>2.6</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E480" s="2" t="s">
         <v>63</v>
@@ -45192,7 +45199,7 @@
         <v>5</v>
       </c>
       <c r="D481" s="2" t="s">
-        <v>1230</v>
+        <v>741</v>
       </c>
       <c r="E481" s="2" t="s">
         <v>63</v>
@@ -45218,7 +45225,7 @@
         <v>1.8</v>
       </c>
       <c r="D482" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E482" s="2" t="s">
         <v>63</v>
@@ -45244,7 +45251,7 @@
         <v>2.6</v>
       </c>
       <c r="D483" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E483" s="2" t="s">
         <v>63</v>
@@ -45270,7 +45277,7 @@
         <v>4</v>
       </c>
       <c r="D484" s="2" t="s">
-        <v>1230</v>
+        <v>741</v>
       </c>
       <c r="E484" s="2" t="s">
         <v>63</v>
@@ -45374,7 +45381,7 @@
         <v>2.15</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E488" s="2" t="s">
         <v>63</v>
@@ -45400,7 +45407,7 @@
         <v>2.15</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E489" s="2" t="s">
         <v>63</v>
@@ -45426,7 +45433,7 @@
         <v>0.24</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>1223</v>
+        <v>317</v>
       </c>
       <c r="E490" s="2" t="s">
         <v>63</v>
@@ -45452,7 +45459,7 @@
         <v>1.8</v>
       </c>
       <c r="D491" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E491" s="2" t="s">
         <v>63</v>
@@ -45478,7 +45485,7 @@
         <v>7.2070000000000007</v>
       </c>
       <c r="D492" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E492" s="2" t="s">
         <v>63</v>
@@ -45530,7 +45537,7 @@
         <v>10.408999999999999</v>
       </c>
       <c r="D494" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E494" s="2" t="s">
         <v>63</v>
@@ -45556,7 +45563,7 @@
         <v>3.6</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E495" s="2" t="s">
         <v>63</v>
@@ -45582,7 +45589,7 @@
         <v>3.6</v>
       </c>
       <c r="D496" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E496" s="2" t="s">
         <v>63</v>
@@ -45608,7 +45615,7 @@
         <v>1</v>
       </c>
       <c r="D497" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E497" s="2" t="s">
         <v>63</v>
@@ -45634,7 +45641,7 @@
         <v>1</v>
       </c>
       <c r="D498" s="2" t="s">
-        <v>1230</v>
+        <v>741</v>
       </c>
       <c r="E498" s="2" t="s">
         <v>63</v>
@@ -45660,7 +45667,7 @@
         <v>1</v>
       </c>
       <c r="D499" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E499" s="2" t="s">
         <v>63</v>
@@ -45686,7 +45693,7 @@
         <v>1</v>
       </c>
       <c r="D500" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E500" s="2" t="s">
         <v>63</v>
@@ -45712,7 +45719,7 @@
         <v>4.4400000000000004</v>
       </c>
       <c r="D501" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E501" s="2" t="s">
         <v>63</v>
@@ -45738,7 +45745,7 @@
         <v>2.2800000000000002</v>
       </c>
       <c r="D502" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E502" s="2" t="s">
         <v>63</v>
@@ -45764,7 +45771,7 @@
         <v>1</v>
       </c>
       <c r="D503" s="2" t="s">
-        <v>1216</v>
+        <v>115</v>
       </c>
       <c r="E503" s="2" t="s">
         <v>63</v>
@@ -45790,7 +45797,7 @@
         <v>3</v>
       </c>
       <c r="D504" s="2" t="s">
-        <v>1230</v>
+        <v>741</v>
       </c>
       <c r="E504" s="2" t="s">
         <v>63</v>
@@ -45816,7 +45823,7 @@
         <v>1.8</v>
       </c>
       <c r="D505" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E505" s="2" t="s">
         <v>63</v>
@@ -45842,7 +45849,7 @@
         <v>3.12</v>
       </c>
       <c r="D506" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E506" s="2" t="s">
         <v>63</v>
@@ -45868,7 +45875,7 @@
         <v>0.88</v>
       </c>
       <c r="D507" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E507" s="2" t="s">
         <v>63</v>
@@ -45894,7 +45901,7 @@
         <v>0.88</v>
       </c>
       <c r="D508" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E508" s="2" t="s">
         <v>63</v>
@@ -45920,7 +45927,7 @@
         <v>0.88</v>
       </c>
       <c r="D509" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E509" s="2" t="s">
         <v>63</v>
@@ -45946,7 +45953,7 @@
         <v>0.44</v>
       </c>
       <c r="D510" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E510" s="2" t="s">
         <v>63</v>
@@ -45972,7 +45979,7 @@
         <v>0.44</v>
       </c>
       <c r="D511" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E511" s="2" t="s">
         <v>63</v>
@@ -45998,7 +46005,7 @@
         <v>0.44</v>
       </c>
       <c r="D512" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E512" s="2" t="s">
         <v>63</v>
@@ -46024,7 +46031,7 @@
         <v>1.7</v>
       </c>
       <c r="D513" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E513" s="2" t="s">
         <v>63</v>
@@ -46050,7 +46057,7 @@
         <v>1.7</v>
       </c>
       <c r="D514" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E514" s="2" t="s">
         <v>63</v>
@@ -46076,7 +46083,7 @@
         <v>1.7</v>
       </c>
       <c r="D515" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E515" s="2" t="s">
         <v>63</v>
@@ -46102,7 +46109,7 @@
         <v>2.6</v>
       </c>
       <c r="D516" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E516" s="2" t="s">
         <v>63</v>
@@ -46128,7 +46135,7 @@
         <v>2.6</v>
       </c>
       <c r="D517" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E517" s="2" t="s">
         <v>63</v>
@@ -46154,7 +46161,7 @@
         <v>2.6</v>
       </c>
       <c r="D518" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E518" s="2" t="s">
         <v>63</v>
@@ -46180,7 +46187,7 @@
         <v>5</v>
       </c>
       <c r="D519" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E519" s="2" t="s">
         <v>63</v>
@@ -46206,7 +46213,7 @@
         <v>3.48</v>
       </c>
       <c r="D520" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E520" s="2" t="s">
         <v>63</v>
@@ -46232,7 +46239,7 @@
         <v>9.92</v>
       </c>
       <c r="D521" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E521" s="2" t="s">
         <v>63</v>
@@ -46258,7 +46265,7 @@
         <v>8.94</v>
       </c>
       <c r="D522" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E522" s="2" t="s">
         <v>63</v>
@@ -46284,7 +46291,7 @@
         <v>6.3</v>
       </c>
       <c r="D523" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E523" s="2" t="s">
         <v>63</v>
@@ -46310,7 +46317,7 @@
         <v>4.3</v>
       </c>
       <c r="D524" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E524" s="2" t="s">
         <v>63</v>
@@ -46336,7 +46343,7 @@
         <v>3.2</v>
       </c>
       <c r="D525" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E525" s="2" t="s">
         <v>63</v>
@@ -46362,7 +46369,7 @@
         <v>7.92</v>
       </c>
       <c r="D526" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E526" s="2" t="s">
         <v>63</v>
@@ -46388,7 +46395,7 @@
         <v>2.62</v>
       </c>
       <c r="D527" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E527" s="2" t="s">
         <v>63</v>
@@ -46414,7 +46421,7 @@
         <v>0.85</v>
       </c>
       <c r="D528" s="2" t="s">
-        <v>1230</v>
+        <v>741</v>
       </c>
       <c r="E528" s="2" t="s">
         <v>63</v>
@@ -46440,7 +46447,7 @@
         <v>2.2400000000000002</v>
       </c>
       <c r="D529" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E529" s="2" t="s">
         <v>63</v>
@@ -46466,7 +46473,7 @@
         <v>7.58</v>
       </c>
       <c r="D530" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E530" s="2" t="s">
         <v>63</v>
@@ -46492,7 +46499,7 @@
         <v>1</v>
       </c>
       <c r="D531" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E531" s="2" t="s">
         <v>63</v>
@@ -46518,7 +46525,7 @@
         <v>1</v>
       </c>
       <c r="D532" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E532" s="2" t="s">
         <v>63</v>
@@ -46544,7 +46551,7 @@
         <v>2.14</v>
       </c>
       <c r="D533" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E533" s="2" t="s">
         <v>63</v>
@@ -46570,7 +46577,7 @@
         <v>1.54</v>
       </c>
       <c r="D534" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E534" s="2" t="s">
         <v>63</v>
@@ -46596,7 +46603,7 @@
         <v>3.14</v>
       </c>
       <c r="D535" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E535" s="2" t="s">
         <v>63</v>
@@ -46622,7 +46629,7 @@
         <v>3.46</v>
       </c>
       <c r="D536" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E536" s="2" t="s">
         <v>63</v>
@@ -46648,7 +46655,7 @@
         <v>0.7</v>
       </c>
       <c r="D537" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E537" s="2" t="s">
         <v>63</v>
@@ -46674,7 +46681,7 @@
         <v>0.7</v>
       </c>
       <c r="D538" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E538" s="2" t="s">
         <v>63</v>
@@ -46700,7 +46707,7 @@
         <v>1.54</v>
       </c>
       <c r="D539" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E539" s="2" t="s">
         <v>63</v>
@@ -46726,7 +46733,7 @@
         <v>2.31</v>
       </c>
       <c r="D540" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E540" s="2" t="s">
         <v>63</v>
@@ -46752,7 +46759,7 @@
         <v>2.31</v>
       </c>
       <c r="D541" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E541" s="2" t="s">
         <v>63</v>
@@ -46778,7 +46785,7 @@
         <v>1.65</v>
       </c>
       <c r="D542" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E542" s="2" t="s">
         <v>63</v>
@@ -46804,7 +46811,7 @@
         <v>1.65</v>
       </c>
       <c r="D543" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E543" s="2" t="s">
         <v>63</v>
@@ -46830,7 +46837,7 @@
         <v>4.5599999999999996</v>
       </c>
       <c r="D544" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E544" s="2" t="s">
         <v>63</v>
@@ -46856,7 +46863,7 @@
         <v>3.92</v>
       </c>
       <c r="D545" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E545" s="2" t="s">
         <v>63</v>
@@ -46882,7 +46889,7 @@
         <v>9.08</v>
       </c>
       <c r="D546" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E546" s="2" t="s">
         <v>63</v>
@@ -46908,7 +46915,7 @@
         <v>1.65</v>
       </c>
       <c r="D547" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E547" s="2" t="s">
         <v>63</v>
@@ -46934,7 +46941,7 @@
         <v>1.54</v>
       </c>
       <c r="D548" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E548" s="2" t="s">
         <v>63</v>
@@ -46960,7 +46967,7 @@
         <v>1.65</v>
       </c>
       <c r="D549" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E549" s="2" t="s">
         <v>63</v>
@@ -46986,7 +46993,7 @@
         <v>9.58</v>
       </c>
       <c r="D550" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E550" s="2" t="s">
         <v>63</v>
@@ -47012,7 +47019,7 @@
         <v>7.75</v>
       </c>
       <c r="D551" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E551" s="2" t="s">
         <v>63</v>
@@ -47038,7 +47045,7 @@
         <v>3.19</v>
       </c>
       <c r="D552" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E552" s="2" t="s">
         <v>63</v>
@@ -47064,7 +47071,7 @@
         <v>5.8</v>
       </c>
       <c r="D553" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E553" s="2" t="s">
         <v>63</v>
@@ -47090,7 +47097,7 @@
         <v>2.98</v>
       </c>
       <c r="D554" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E554" s="2" t="s">
         <v>63</v>
@@ -47116,7 +47123,7 @@
         <v>6.83</v>
       </c>
       <c r="D555" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E555" s="2" t="s">
         <v>63</v>
@@ -47142,7 +47149,7 @@
         <v>1</v>
       </c>
       <c r="D556" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E556" s="2" t="s">
         <v>63</v>
@@ -47168,7 +47175,7 @@
         <v>1.78</v>
       </c>
       <c r="D557" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E557" s="2" t="s">
         <v>63</v>
@@ -47194,7 +47201,7 @@
         <v>1.78</v>
       </c>
       <c r="D558" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E558" s="2" t="s">
         <v>63</v>
@@ -47220,7 +47227,7 @@
         <v>1.78</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E559" s="2" t="s">
         <v>63</v>
@@ -47246,7 +47253,7 @@
         <v>1.78</v>
       </c>
       <c r="D560" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E560" s="2" t="s">
         <v>63</v>
@@ -47272,7 +47279,7 @@
         <v>6.68</v>
       </c>
       <c r="D561" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E561" s="2" t="s">
         <v>63</v>
@@ -47298,7 +47305,7 @@
         <v>3.9</v>
       </c>
       <c r="D562" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E562" s="2" t="s">
         <v>63</v>
@@ -47324,7 +47331,7 @@
         <v>2.7</v>
       </c>
       <c r="D563" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E563" s="2" t="s">
         <v>63</v>
@@ -47350,7 +47357,7 @@
         <v>7.56</v>
       </c>
       <c r="D564" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E564" s="2" t="s">
         <v>63</v>
@@ -47376,7 +47383,7 @@
         <v>3.56</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E565" s="2" t="s">
         <v>63</v>
@@ -47402,7 +47409,7 @@
         <v>0.25</v>
       </c>
       <c r="D566" s="2" t="s">
-        <v>1223</v>
+        <v>317</v>
       </c>
       <c r="E566" s="2" t="s">
         <v>63</v>
@@ -47428,7 +47435,7 @@
         <v>7.12</v>
       </c>
       <c r="D567" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E567" s="2" t="s">
         <v>63</v>
@@ -47454,7 +47461,7 @@
         <v>9.02</v>
       </c>
       <c r="D568" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E568" s="2" t="s">
         <v>63</v>
@@ -47480,7 +47487,7 @@
         <v>4</v>
       </c>
       <c r="D569" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E569" s="2" t="s">
         <v>63</v>
@@ -47506,7 +47513,7 @@
         <v>8.6</v>
       </c>
       <c r="D570" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E570" s="2" t="s">
         <v>63</v>
@@ -47532,7 +47539,7 @@
         <v>3.7800000000000002</v>
       </c>
       <c r="D571" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E571" s="2" t="s">
         <v>63</v>
@@ -47558,7 +47565,7 @@
         <v>1</v>
       </c>
       <c r="D572" s="2" t="s">
-        <v>1224</v>
+        <v>275</v>
       </c>
       <c r="E572" s="2" t="s">
         <v>63</v>
@@ -47584,7 +47591,7 @@
         <v>8.6</v>
       </c>
       <c r="D573" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E573" s="2" t="s">
         <v>63</v>
@@ -47610,7 +47617,7 @@
         <v>6</v>
       </c>
       <c r="D574" s="2" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="E574" s="2" t="s">
         <v>63</v>
@@ -47636,7 +47643,7 @@
         <v>6.43</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E575" s="2" t="s">
         <v>63</v>
@@ -47662,7 +47669,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="D576" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E576" s="2" t="s">
         <v>63</v>
@@ -47688,7 +47695,7 @@
         <v>0.2</v>
       </c>
       <c r="D577" s="2" t="s">
-        <v>1223</v>
+        <v>317</v>
       </c>
       <c r="E577" s="2" t="s">
         <v>63</v>
@@ -47714,7 +47721,7 @@
         <v>0.35</v>
       </c>
       <c r="D578" s="2" t="s">
-        <v>1223</v>
+        <v>317</v>
       </c>
       <c r="E578" s="2" t="s">
         <v>63</v>
@@ -47740,7 +47747,7 @@
         <v>4.42</v>
       </c>
       <c r="D579" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E579" s="2" t="s">
         <v>63</v>
@@ -47766,7 +47773,7 @@
         <v>4.09</v>
       </c>
       <c r="D580" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E580" s="2" t="s">
         <v>63</v>
@@ -47792,7 +47799,7 @@
         <v>8.9</v>
       </c>
       <c r="D581" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E581" s="2" t="s">
         <v>63</v>
@@ -47818,7 +47825,7 @@
         <v>1.61</v>
       </c>
       <c r="D582" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E582" s="2" t="s">
         <v>63</v>
@@ -47844,7 +47851,7 @@
         <v>1.61</v>
       </c>
       <c r="D583" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E583" s="2" t="s">
         <v>63</v>
@@ -47870,7 +47877,7 @@
         <v>2.9699999999999998</v>
       </c>
       <c r="D584" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E584" s="2" t="s">
         <v>63</v>
@@ -47896,7 +47903,7 @@
         <v>0</v>
       </c>
       <c r="D585" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E585" s="2" t="s">
         <v>30</v>
@@ -47922,7 +47929,7 @@
         <v>5</v>
       </c>
       <c r="D586" s="2" t="s">
-        <v>1220</v>
+        <v>154</v>
       </c>
       <c r="E586" s="2" t="s">
         <v>63</v>
@@ -47948,7 +47955,7 @@
         <v>2.7</v>
       </c>
       <c r="D587" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E587" s="2" t="s">
         <v>63</v>
@@ -47974,7 +47981,7 @@
         <v>3.36</v>
       </c>
       <c r="D588" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E588" s="2" t="s">
         <v>63</v>
@@ -48000,7 +48007,7 @@
         <v>0.9</v>
       </c>
       <c r="D589" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E589" s="2" t="s">
         <v>63</v>
@@ -48026,7 +48033,7 @@
         <v>0.9</v>
       </c>
       <c r="D590" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E590" s="2" t="s">
         <v>63</v>
@@ -48052,7 +48059,7 @@
         <v>0.9</v>
       </c>
       <c r="D591" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E591" s="2" t="s">
         <v>63</v>
@@ -48078,7 +48085,7 @@
         <v>3.5</v>
       </c>
       <c r="D592" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E592" s="2" t="s">
         <v>63</v>
@@ -48104,7 +48111,7 @@
         <v>4.0600000000000005</v>
       </c>
       <c r="D593" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E593" s="2" t="s">
         <v>63</v>
@@ -48130,7 +48137,7 @@
         <v>1.2</v>
       </c>
       <c r="D594" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E594" s="2" t="s">
         <v>63</v>
@@ -48156,7 +48163,7 @@
         <v>1.2</v>
       </c>
       <c r="D595" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E595" s="2" t="s">
         <v>63</v>
@@ -48182,7 +48189,7 @@
         <v>1.9</v>
       </c>
       <c r="D596" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E596" s="2" t="s">
         <v>63</v>
@@ -48208,7 +48215,7 @@
         <v>1.9</v>
       </c>
       <c r="D597" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E597" s="2" t="s">
         <v>63</v>
@@ -48234,7 +48241,7 @@
         <v>1.9</v>
       </c>
       <c r="D598" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E598" s="2" t="s">
         <v>63</v>
@@ -48260,7 +48267,7 @@
         <v>1.3</v>
       </c>
       <c r="D599" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E599" s="2" t="s">
         <v>63</v>
@@ -48286,7 +48293,7 @@
         <v>1.3</v>
       </c>
       <c r="D600" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E600" s="2" t="s">
         <v>63</v>
@@ -48312,7 +48319,7 @@
         <v>1.3</v>
       </c>
       <c r="D601" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E601" s="2" t="s">
         <v>63</v>
@@ -48338,7 +48345,7 @@
         <v>7.6000000000000005</v>
       </c>
       <c r="D602" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E602" s="2" t="s">
         <v>63</v>
@@ -48364,7 +48371,7 @@
         <v>1.2</v>
       </c>
       <c r="D603" s="2" t="s">
-        <v>1222</v>
+        <v>208</v>
       </c>
       <c r="E603" s="2" t="s">
         <v>63</v>
@@ -48390,7 +48397,7 @@
         <v>1</v>
       </c>
       <c r="D604" s="2" t="s">
-        <v>1226</v>
+        <v>256</v>
       </c>
       <c r="E604" s="2" t="s">
         <v>63</v>
@@ -48416,7 +48423,7 @@
         <v>1</v>
       </c>
       <c r="D605" s="2" t="s">
-        <v>1226</v>
+        <v>256</v>
       </c>
       <c r="E605" s="2" t="s">
         <v>63</v>
@@ -48442,7 +48449,7 @@
         <v>1</v>
       </c>
       <c r="D606" s="2" t="s">
-        <v>1226</v>
+        <v>256</v>
       </c>
       <c r="E606" s="2" t="s">
         <v>63</v>
@@ -48468,7 +48475,7 @@
         <v>2.7</v>
       </c>
       <c r="D607" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E607" s="2" t="s">
         <v>63</v>
@@ -48494,7 +48501,7 @@
         <v>2.7</v>
       </c>
       <c r="D608" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E608" s="2" t="s">
         <v>63</v>
@@ -48520,7 +48527,7 @@
         <v>2.7</v>
       </c>
       <c r="D609" s="2" t="s">
-        <v>1217</v>
+        <v>124</v>
       </c>
       <c r="E609" s="2" t="s">
         <v>63</v>
@@ -48546,7 +48553,7 @@
         <v>5.7</v>
       </c>
       <c r="D610" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E610" s="2" t="s">
         <v>63</v>
@@ -48572,7 +48579,7 @@
         <v>4.25</v>
       </c>
       <c r="D611" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E611" s="2" t="s">
         <v>63</v>
@@ -49222,7 +49229,7 @@
         <v>2.8</v>
       </c>
       <c r="D636" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E636" s="2" t="s">
         <v>63</v>
@@ -49248,7 +49255,7 @@
         <v>3.22</v>
       </c>
       <c r="D637" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E637" s="2" t="s">
         <v>63</v>
@@ -49274,7 +49281,7 @@
         <v>3.22</v>
       </c>
       <c r="D638" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E638" s="2" t="s">
         <v>63</v>
@@ -49300,7 +49307,7 @@
         <v>2.6001000000000003</v>
       </c>
       <c r="D639" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E639" s="2" t="s">
         <v>63</v>
@@ -49326,7 +49333,7 @@
         <v>2.8001</v>
       </c>
       <c r="D640" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E640" s="2" t="s">
         <v>63</v>
@@ -49352,7 +49359,7 @@
         <v>3.6</v>
       </c>
       <c r="D641" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E641" s="2" t="s">
         <v>63</v>
@@ -49378,7 +49385,7 @@
         <v>2.6</v>
       </c>
       <c r="D642" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E642" s="2" t="s">
         <v>63</v>
@@ -49404,7 +49411,7 @@
         <v>3.96</v>
       </c>
       <c r="D643" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E643" s="2" t="s">
         <v>63</v>
@@ -49430,7 +49437,7 @@
         <v>6.16</v>
       </c>
       <c r="D644" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E644" s="2" t="s">
         <v>63</v>
@@ -49456,7 +49463,7 @@
         <v>7.7</v>
       </c>
       <c r="D645" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E645" s="2" t="s">
         <v>63</v>
@@ -50730,7 +50737,7 @@
         <v>0.88</v>
       </c>
       <c r="D694" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E694" s="2" t="s">
         <v>63</v>
@@ -50756,7 +50763,7 @@
         <v>1.76</v>
       </c>
       <c r="D695" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E695" s="2" t="s">
         <v>63</v>
@@ -50782,7 +50789,7 @@
         <v>1.2</v>
       </c>
       <c r="D696" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E696" s="2" t="s">
         <v>63</v>
@@ -50808,7 +50815,7 @@
         <v>1.75</v>
       </c>
       <c r="D697" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E697" s="2" t="s">
         <v>63</v>
@@ -50834,7 +50841,7 @@
         <v>1.75</v>
       </c>
       <c r="D698" s="2" t="s">
-        <v>1214</v>
+        <v>60</v>
       </c>
       <c r="E698" s="2" t="s">
         <v>63</v>
@@ -50860,7 +50867,7 @@
         <v>8.6</v>
       </c>
       <c r="D699" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E699" s="2" t="s">
         <v>63</v>
@@ -50886,7 +50893,7 @@
         <v>1.7600100000000001</v>
       </c>
       <c r="D700" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E700" s="2" t="s">
         <v>63</v>
@@ -50912,7 +50919,7 @@
         <v>1.9000999999999999</v>
       </c>
       <c r="D701" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E701" s="2" t="s">
         <v>63</v>
@@ -50938,7 +50945,7 @@
         <v>3.6</v>
       </c>
       <c r="D702" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E702" s="2" t="s">
         <v>63</v>
@@ -50964,7 +50971,7 @@
         <v>6.1600999999999999</v>
       </c>
       <c r="D703" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E703" s="2" t="s">
         <v>63</v>
@@ -50990,7 +50997,7 @@
         <v>3.8001999999999998</v>
       </c>
       <c r="D704" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E704" s="2" t="s">
         <v>63</v>
@@ -51016,7 +51023,7 @@
         <v>4.4802999999999997</v>
       </c>
       <c r="D705" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E705" s="2" t="s">
         <v>63</v>
@@ -51042,7 +51049,7 @@
         <v>5.18</v>
       </c>
       <c r="D706" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E706" s="2" t="s">
         <v>63</v>
@@ -51068,7 +51075,7 @@
         <v>1.0004999999999999</v>
       </c>
       <c r="D707" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E707" s="2" t="s">
         <v>63</v>
@@ -51094,7 +51101,7 @@
         <v>1.0004999999999999</v>
       </c>
       <c r="D708" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E708" s="2" t="s">
         <v>63</v>
@@ -51120,7 +51127,7 @@
         <v>1.32</v>
       </c>
       <c r="D709" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E709" s="2" t="s">
         <v>63</v>
@@ -52290,7 +52297,7 @@
         <v>3.14</v>
       </c>
       <c r="D754" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E754" s="2" t="s">
         <v>63</v>
@@ -52316,7 +52323,7 @@
         <v>3.97</v>
       </c>
       <c r="D755" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E755" s="2" t="s">
         <v>63</v>
@@ -52420,7 +52427,7 @@
         <v>2.5499999999999998</v>
       </c>
       <c r="D759" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E759" s="2" t="s">
         <v>63</v>
@@ -52446,7 +52453,7 @@
         <v>9.36</v>
       </c>
       <c r="D760" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E760" s="2" t="s">
         <v>63</v>
@@ -52472,7 +52479,7 @@
         <v>9.48</v>
       </c>
       <c r="D761" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E761" s="2" t="s">
         <v>63</v>
@@ -52498,7 +52505,7 @@
         <v>3.3</v>
       </c>
       <c r="D762" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E762" s="2" t="s">
         <v>63</v>
@@ -52524,7 +52531,7 @@
         <v>2.7</v>
       </c>
       <c r="D763" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E763" s="2" t="s">
         <v>63</v>
@@ -52550,7 +52557,7 @@
         <v>7.08</v>
       </c>
       <c r="D764" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E764" s="2" t="s">
         <v>63</v>
@@ -52576,7 +52583,7 @@
         <v>10.6</v>
       </c>
       <c r="D765" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E765" s="2" t="s">
         <v>63</v>
@@ -52602,7 +52609,7 @@
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="D766" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E766" s="2" t="s">
         <v>63</v>
@@ -52628,7 +52635,7 @@
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="D767" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E767" s="2" t="s">
         <v>63</v>
@@ -52654,7 +52661,7 @@
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="D768" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E768" s="2" t="s">
         <v>63</v>
@@ -52680,7 +52687,7 @@
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="D769" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E769" s="2" t="s">
         <v>63</v>
@@ -52706,7 +52713,7 @@
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="D770" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E770" s="2" t="s">
         <v>63</v>
@@ -52732,7 +52739,7 @@
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="D771" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E771" s="2" t="s">
         <v>63</v>
@@ -52758,7 +52765,7 @@
         <v>7.62</v>
       </c>
       <c r="D772" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E772" s="2" t="s">
         <v>63</v>
@@ -52784,7 +52791,7 @@
         <v>1.76</v>
       </c>
       <c r="D773" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E773" s="2" t="s">
         <v>63</v>
@@ -52810,7 +52817,7 @@
         <v>3.23</v>
       </c>
       <c r="D774" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E774" s="2" t="s">
         <v>63</v>
@@ -52836,7 +52843,7 @@
         <v>2.46</v>
       </c>
       <c r="D775" s="2" t="s">
-        <v>1229</v>
+        <v>29</v>
       </c>
       <c r="E775" s="2" t="s">
         <v>63</v>
@@ -52862,7 +52869,7 @@
         <v>1</v>
       </c>
       <c r="D776" s="2" t="s">
-        <v>1230</v>
+        <v>741</v>
       </c>
       <c r="E776" s="2" t="s">
         <v>63</v>
@@ -53174,7 +53181,7 @@
         <v>3</v>
       </c>
       <c r="D788" s="2" t="s">
-        <v>1230</v>
+        <v>741</v>
       </c>
       <c r="E788" s="2" t="s">
         <v>63</v>
@@ -53200,7 +53207,7 @@
         <v>5</v>
       </c>
       <c r="D789" s="2" t="s">
-        <v>1230</v>
+        <v>741</v>
       </c>
       <c r="E789" s="2" t="s">
         <v>63</v>
@@ -53460,7 +53467,7 @@
         <v>0.75</v>
       </c>
       <c r="D799" s="2" t="s">
-        <v>1228</v>
+        <v>310</v>
       </c>
       <c r="E799" s="2" t="s">
         <v>63</v>
@@ -53486,7 +53493,7 @@
         <v>0.75</v>
       </c>
       <c r="D800" s="2" t="s">
-        <v>1228</v>
+        <v>310</v>
       </c>
       <c r="E800" s="2" t="s">
         <v>63</v>
@@ -53512,7 +53519,7 @@
         <v>0.75</v>
       </c>
       <c r="D801" s="2" t="s">
-        <v>1228</v>
+        <v>310</v>
       </c>
       <c r="E801" s="2" t="s">
         <v>63</v>
@@ -54244,15 +54251,15 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1 A962:A1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A962:H1008">
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>$E962="AKTIV"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E962:E1008">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"AKTIV"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/produkte+.xlsx
+++ b/produkte+.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\app_iphone_shitjet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA34E144-C4E7-4FF5-9639-E3DC3423F157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA7BD64-1195-47A7-8BB5-C9EA76467FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F852DC8A-6273-46A5-80EE-4F7A2FD95859}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="785" activeTab="1" xr2:uid="{F852DC8A-6273-46A5-80EE-4F7A2FD95859}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32699,7 +32699,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
-    <col min="2" max="2" width="63.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="41" style="2" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="2"/>
     <col min="4" max="4" width="8.42578125" style="3" customWidth="1"/>
     <col min="5" max="5" width="9.5703125" style="2" customWidth="1"/>

--- a/produkte+.xlsx
+++ b/produkte+.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\app_iphone_shitjet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA7BD64-1195-47A7-8BB5-C9EA76467FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A2C820-2E5C-4BAC-BD6B-50D8B16BE0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="785" activeTab="1" xr2:uid="{F852DC8A-6273-46A5-80EE-4F7A2FD95859}"/>
   </bookViews>
@@ -5454,14 +5454,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Per cent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill>
@@ -32666,25 +32659,25 @@
     <mergeCell ref="E5:E6"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7:H1013">
-    <cfRule type="expression" dxfId="7" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>$E7="AKTIV"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:E1013">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
       <formula>"AKTIV"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H4">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",H3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54251,15 +54244,15 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1 A962:A1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A962:H1008">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>$E962="AKTIV"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E962:E1008">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"AKTIV"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/produkte+.xlsx
+++ b/produkte+.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\app_iphone_shitjet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A2C820-2E5C-4BAC-BD6B-50D8B16BE0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3357B25B-4AB0-424B-80F4-FFB0F363ADDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="785" activeTab="1" xr2:uid="{F852DC8A-6273-46A5-80EE-4F7A2FD95859}"/>
   </bookViews>
@@ -17,6 +17,9 @@
     <sheet name="produktet" sheetId="2" r:id="rId2"/>
     <sheet name="kat_prod" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">produktet!$A$1:$H$801</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -32897,7 +32900,7 @@
         <v>29</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F8" s="2">
         <v>33.001108472371804</v>
@@ -33157,7 +33160,7 @@
         <v>66</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="F18" s="2">
         <v>50.624474066666671</v>
@@ -33183,7 +33186,7 @@
         <v>66</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="F19" s="2">
         <v>50.519174066666665</v>
@@ -33287,7 +33290,7 @@
         <v>66</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F23" s="2">
         <v>46.127238388888884</v>
@@ -33755,7 +33758,7 @@
         <v>60</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F41" s="2">
         <v>96.693214240056832</v>
@@ -33859,7 +33862,7 @@
         <v>115</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F45" s="2">
         <v>56.370013950000001</v>
@@ -34249,7 +34252,7 @@
         <v>154</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="F60" s="2">
         <v>72.177727683877222</v>
@@ -34457,7 +34460,7 @@
         <v>154</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F68" s="2">
         <v>64.773018145212504</v>
@@ -34561,7 +34564,7 @@
         <v>154</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="F72" s="2">
         <v>69.217969293056925</v>
@@ -34795,7 +34798,7 @@
         <v>193</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F81" s="2">
         <v>11.057649999999999</v>
@@ -34899,7 +34902,7 @@
         <v>193</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F85" s="2">
         <v>22.210187917999999</v>
@@ -35445,7 +35448,7 @@
         <v>208</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F106" s="2">
         <v>35.115006038064756</v>
@@ -35471,7 +35474,7 @@
         <v>208</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F107" s="2">
         <v>37.763597169913488</v>
@@ -35497,7 +35500,7 @@
         <v>208</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F108" s="2">
         <v>36.855063137106917</v>
@@ -35523,7 +35526,7 @@
         <v>256</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="F109" s="2">
         <v>48.935125966766606</v>
@@ -35939,7 +35942,7 @@
         <v>275</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F125" s="2">
         <v>21.859728226163522</v>
@@ -35965,7 +35968,7 @@
         <v>275</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F126" s="2">
         <v>21.77765939942369</v>
@@ -35991,7 +35994,7 @@
         <v>275</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F127" s="2">
         <v>23.269164948427676</v>
@@ -36043,7 +36046,7 @@
         <v>275</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="F129" s="2">
         <v>29.032302749999999</v>
@@ -36641,7 +36644,7 @@
         <v>29</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="F152" s="2">
         <v>96.380582630207726</v>
@@ -36979,7 +36982,7 @@
         <v>60</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="F165" s="2">
         <v>84.254519166666654</v>
@@ -37005,7 +37008,7 @@
         <v>66</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F166" s="2">
         <v>59.085680000000004</v>
@@ -37057,7 +37060,7 @@
         <v>193</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F168" s="2">
         <v>21.449844201333327</v>
@@ -37109,7 +37112,7 @@
         <v>193</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F170" s="2">
         <v>17.368932370653855</v>
@@ -37135,7 +37138,7 @@
         <v>386</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="F171" s="2">
         <v>77.750096747918846</v>
@@ -38175,7 +38178,7 @@
         <v>60</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F211" s="2">
         <v>124.65077593224629</v>
@@ -38201,7 +38204,7 @@
         <v>60</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F212" s="2">
         <v>128.94117148413841</v>
@@ -38487,7 +38490,7 @@
         <v>275</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F223" s="2">
         <v>29.332299990000003</v>
@@ -38643,7 +38646,7 @@
         <v>29</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F229" s="2">
         <v>120.21090998507643</v>
@@ -39553,7 +39556,7 @@
         <v>29</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F264" s="2">
         <v>92.40692795271714</v>
@@ -39579,7 +39582,7 @@
         <v>29</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F265" s="2">
         <v>89.710961257765149</v>
@@ -39865,7 +39868,7 @@
         <v>29</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F276" s="2">
         <v>117.86919624567311</v>
@@ -40021,7 +40024,7 @@
         <v>29</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="F282" s="2">
         <v>84.665662263782451</v>
@@ -40073,7 +40076,7 @@
         <v>29</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F284" s="2">
         <v>121.07864808945558</v>
@@ -40099,7 +40102,7 @@
         <v>29</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F285" s="2">
         <v>121.75831968437552</v>
@@ -40125,7 +40128,7 @@
         <v>29</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F286" s="2">
         <v>118.54743741000226</v>
@@ -40333,7 +40336,7 @@
         <v>29</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F294" s="2">
         <v>111.72998346197306</v>
@@ -40385,7 +40388,7 @@
         <v>29</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="F296" s="2">
         <v>83.970723942768956</v>
@@ -40437,7 +40440,7 @@
         <v>29</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F298" s="2">
         <v>60.456654937804103</v>
@@ -40879,7 +40882,7 @@
         <v>29</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F315" s="2">
         <v>116.7615827886696</v>
@@ -45117,7 +45120,7 @@
         <v>741</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F478" s="2">
         <v>116.99640000000001</v>
@@ -45455,7 +45458,7 @@
         <v>60</v>
       </c>
       <c r="E491" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F491" s="2">
         <v>100.55030323019176</v>
@@ -45481,7 +45484,7 @@
         <v>29</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F492" s="2">
         <v>118.97119843111628</v>
@@ -45689,7 +45692,7 @@
         <v>60</v>
       </c>
       <c r="E500" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F500" s="2">
         <v>99.019729999999996</v>
@@ -45741,7 +45744,7 @@
         <v>29</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F502" s="2">
         <v>104.57172194013738</v>
@@ -46235,7 +46238,7 @@
         <v>29</v>
       </c>
       <c r="E521" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F521" s="2">
         <v>101.99865319667479</v>
@@ -46261,7 +46264,7 @@
         <v>29</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F522" s="2">
         <v>117.7886621268978</v>
@@ -46339,7 +46342,7 @@
         <v>60</v>
       </c>
       <c r="E525" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F525" s="2">
         <v>130.34785484666668</v>
@@ -46365,7 +46368,7 @@
         <v>29</v>
       </c>
       <c r="E526" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F526" s="2">
         <v>99.30575781655466</v>
@@ -46391,7 +46394,7 @@
         <v>29</v>
       </c>
       <c r="E527" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F527" s="2">
         <v>93.922659395860876</v>
@@ -46417,7 +46420,7 @@
         <v>741</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F528" s="2">
         <v>120</v>
@@ -46495,7 +46498,7 @@
         <v>154</v>
       </c>
       <c r="E531" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F531" s="2">
         <v>45.31136544071596</v>
@@ -46521,7 +46524,7 @@
         <v>124</v>
       </c>
       <c r="E532" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F532" s="2">
         <v>68.099143384467737</v>
@@ -46599,7 +46602,7 @@
         <v>29</v>
       </c>
       <c r="E535" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F535" s="2">
         <v>72.431021228253826</v>
@@ -46625,7 +46628,7 @@
         <v>29</v>
       </c>
       <c r="E536" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F536" s="2">
         <v>97.097483608636153</v>
@@ -46859,7 +46862,7 @@
         <v>29</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F545" s="2">
         <v>93.032282191167795</v>
@@ -47015,7 +47018,7 @@
         <v>29</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F551" s="2">
         <v>113.79447700345956</v>
@@ -47041,7 +47044,7 @@
         <v>29</v>
       </c>
       <c r="E552" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F552" s="2">
         <v>91.407339926914247</v>
@@ -47145,7 +47148,7 @@
         <v>275</v>
       </c>
       <c r="E556" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F556" s="2">
         <v>601.39</v>
@@ -47223,7 +47226,7 @@
         <v>154</v>
       </c>
       <c r="E559" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F559" s="2">
         <v>74.150849388728247</v>
@@ -47639,7 +47642,7 @@
         <v>29</v>
       </c>
       <c r="E575" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F575" s="2">
         <v>117.83905620755102</v>
@@ -47769,7 +47772,7 @@
         <v>29</v>
       </c>
       <c r="E580" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F580" s="2">
         <v>84.546377217205148</v>
@@ -48601,7 +48604,7 @@
         <v>268</v>
       </c>
       <c r="E612" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F612" s="2">
         <v>38.879999999999995</v>
@@ -48627,7 +48630,7 @@
         <v>268</v>
       </c>
       <c r="E613" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F613" s="2">
         <v>38.879999999999995</v>
@@ -48653,7 +48656,7 @@
         <v>268</v>
       </c>
       <c r="E614" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F614" s="2">
         <v>38.879999999999995</v>
@@ -48679,7 +48682,7 @@
         <v>268</v>
       </c>
       <c r="E615" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F615" s="2">
         <v>38.879999999999995</v>
@@ -48705,7 +48708,7 @@
         <v>268</v>
       </c>
       <c r="E616" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F616" s="2">
         <v>34.019999999999996</v>
@@ -48731,7 +48734,7 @@
         <v>268</v>
       </c>
       <c r="E617" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F617" s="2">
         <v>34.019999999999996</v>
@@ -48757,7 +48760,7 @@
         <v>268</v>
       </c>
       <c r="E618" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F618" s="2">
         <v>34.019999999999996</v>
@@ -48783,7 +48786,7 @@
         <v>268</v>
       </c>
       <c r="E619" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F619" s="2">
         <v>74.049869999999999</v>
@@ -48809,7 +48812,7 @@
         <v>268</v>
       </c>
       <c r="E620" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F620" s="2">
         <v>64.8</v>
@@ -48835,7 +48838,7 @@
         <v>268</v>
       </c>
       <c r="E621" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F621" s="2">
         <v>64.8</v>
@@ -48861,7 +48864,7 @@
         <v>268</v>
       </c>
       <c r="E622" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F622" s="2">
         <v>89.100000000000009</v>
@@ -48887,7 +48890,7 @@
         <v>268</v>
       </c>
       <c r="E623" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F623" s="2">
         <v>89.100000000000009</v>
@@ -48913,7 +48916,7 @@
         <v>268</v>
       </c>
       <c r="E624" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F624" s="2">
         <v>89.100000000000009</v>
@@ -48939,7 +48942,7 @@
         <v>268</v>
       </c>
       <c r="E625" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F625" s="2">
         <v>117.45</v>
@@ -48965,7 +48968,7 @@
         <v>268</v>
       </c>
       <c r="E626" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F626" s="2">
         <v>117.45</v>
@@ -48991,7 +48994,7 @@
         <v>268</v>
       </c>
       <c r="E627" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F627" s="2">
         <v>117.45</v>
@@ -49017,7 +49020,7 @@
         <v>268</v>
       </c>
       <c r="E628" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F628" s="2">
         <v>40.5</v>
@@ -49043,7 +49046,7 @@
         <v>268</v>
       </c>
       <c r="E629" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F629" s="2">
         <v>40.5</v>
@@ -49069,7 +49072,7 @@
         <v>268</v>
       </c>
       <c r="E630" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F630" s="2">
         <v>40.5</v>
@@ -49095,7 +49098,7 @@
         <v>268</v>
       </c>
       <c r="E631" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F631" s="2">
         <v>40.5</v>
@@ -49121,7 +49124,7 @@
         <v>268</v>
       </c>
       <c r="E632" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F632" s="2">
         <v>40.5</v>
@@ -49147,7 +49150,7 @@
         <v>268</v>
       </c>
       <c r="E633" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F633" s="2">
         <v>36.450000000000003</v>
@@ -49173,7 +49176,7 @@
         <v>268</v>
       </c>
       <c r="E634" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F634" s="2">
         <v>36.450000000000003</v>
@@ -49199,7 +49202,7 @@
         <v>268</v>
       </c>
       <c r="E635" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F635" s="2">
         <v>36.450000000000003</v>
@@ -49303,7 +49306,7 @@
         <v>29</v>
       </c>
       <c r="E639" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F639" s="2">
         <v>110.87876766705554</v>
@@ -49381,7 +49384,7 @@
         <v>60</v>
       </c>
       <c r="E642" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F642" s="2">
         <v>99.615239204059833</v>
@@ -49485,7 +49488,7 @@
         <v>268</v>
       </c>
       <c r="E646" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F646" s="2">
         <v>67.45</v>
@@ -49511,7 +49514,7 @@
         <v>268</v>
       </c>
       <c r="E647" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F647" s="2">
         <v>114</v>
@@ -49537,7 +49540,7 @@
         <v>268</v>
       </c>
       <c r="E648" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F648" s="2">
         <v>22.8</v>
@@ -49563,7 +49566,7 @@
         <v>268</v>
       </c>
       <c r="E649" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F649" s="2">
         <v>42.75</v>
@@ -49589,7 +49592,7 @@
         <v>268</v>
       </c>
       <c r="E650" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F650" s="2">
         <v>39.9</v>
@@ -49615,7 +49618,7 @@
         <v>268</v>
       </c>
       <c r="E651" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F651" s="2">
         <v>850.24999999999989</v>
@@ -49641,7 +49644,7 @@
         <v>268</v>
       </c>
       <c r="E652" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F652" s="2">
         <v>660.25</v>
@@ -49667,7 +49670,7 @@
         <v>268</v>
       </c>
       <c r="E653" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F653" s="2">
         <v>593.75</v>
@@ -49693,7 +49696,7 @@
         <v>268</v>
       </c>
       <c r="E654" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F654" s="2">
         <v>660.25</v>
@@ -49719,7 +49722,7 @@
         <v>268</v>
       </c>
       <c r="E655" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F655" s="2">
         <v>299.25</v>
@@ -49745,7 +49748,7 @@
         <v>268</v>
       </c>
       <c r="E656" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F656" s="2">
         <v>104.50000000000001</v>
@@ -49771,7 +49774,7 @@
         <v>268</v>
       </c>
       <c r="E657" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F657" s="2">
         <v>80.75</v>
@@ -49797,7 +49800,7 @@
         <v>268</v>
       </c>
       <c r="E658" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F658" s="2">
         <v>223.25</v>
@@ -49823,7 +49826,7 @@
         <v>268</v>
       </c>
       <c r="E659" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F659" s="2">
         <v>61.75</v>
@@ -49849,7 +49852,7 @@
         <v>268</v>
       </c>
       <c r="E660" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F660" s="2">
         <v>85.5</v>
@@ -49875,7 +49878,7 @@
         <v>268</v>
       </c>
       <c r="E661" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F661" s="2">
         <v>47.5</v>
@@ -49901,7 +49904,7 @@
         <v>268</v>
       </c>
       <c r="E662" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F662" s="2">
         <v>118.75</v>
@@ -49927,7 +49930,7 @@
         <v>268</v>
       </c>
       <c r="E663" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F663" s="2">
         <v>152</v>
@@ -49953,7 +49956,7 @@
         <v>268</v>
       </c>
       <c r="E664" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F664" s="2">
         <v>42.75</v>
@@ -49979,7 +49982,7 @@
         <v>268</v>
       </c>
       <c r="E665" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F665" s="2">
         <v>76</v>
@@ -50005,7 +50008,7 @@
         <v>268</v>
       </c>
       <c r="E666" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F666" s="2">
         <v>52.250000000000007</v>
@@ -50031,7 +50034,7 @@
         <v>268</v>
       </c>
       <c r="E667" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F667" s="2">
         <v>76</v>
@@ -50057,7 +50060,7 @@
         <v>268</v>
       </c>
       <c r="E668" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F668" s="2">
         <v>61.75</v>
@@ -50083,7 +50086,7 @@
         <v>268</v>
       </c>
       <c r="E669" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F669" s="2">
         <v>67.45</v>
@@ -50109,7 +50112,7 @@
         <v>268</v>
       </c>
       <c r="E670" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F670" s="2">
         <v>71.25</v>
@@ -50135,7 +50138,7 @@
         <v>268</v>
       </c>
       <c r="E671" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F671" s="2">
         <v>42.75</v>
@@ -50161,7 +50164,7 @@
         <v>268</v>
       </c>
       <c r="E672" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F672" s="2">
         <v>42.75</v>
@@ -50187,7 +50190,7 @@
         <v>268</v>
       </c>
       <c r="E673" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F673" s="2">
         <v>33.25</v>
@@ -50213,7 +50216,7 @@
         <v>268</v>
       </c>
       <c r="E674" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F674" s="2">
         <v>41.8</v>
@@ -50239,7 +50242,7 @@
         <v>268</v>
       </c>
       <c r="E675" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F675" s="2">
         <v>39.9</v>
@@ -50265,7 +50268,7 @@
         <v>268</v>
       </c>
       <c r="E676" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F676" s="2">
         <v>356.25</v>
@@ -50291,7 +50294,7 @@
         <v>268</v>
       </c>
       <c r="E677" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F677" s="2">
         <v>612.75</v>
@@ -50317,7 +50320,7 @@
         <v>268</v>
       </c>
       <c r="E678" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F678" s="2">
         <v>593.75</v>
@@ -50343,7 +50346,7 @@
         <v>268</v>
       </c>
       <c r="E679" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F679" s="2">
         <v>327.75</v>
@@ -50369,7 +50372,7 @@
         <v>268</v>
       </c>
       <c r="E680" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F680" s="2">
         <v>166.25</v>
@@ -50395,7 +50398,7 @@
         <v>268</v>
       </c>
       <c r="E681" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F681" s="2">
         <v>104.50000000000001</v>
@@ -50421,7 +50424,7 @@
         <v>268</v>
       </c>
       <c r="E682" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F682" s="2">
         <v>118.75</v>
@@ -50447,7 +50450,7 @@
         <v>268</v>
       </c>
       <c r="E683" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F683" s="2">
         <v>52.250000000000007</v>
@@ -50473,7 +50476,7 @@
         <v>268</v>
       </c>
       <c r="E684" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F684" s="2">
         <v>52.250000000000007</v>
@@ -50499,7 +50502,7 @@
         <v>268</v>
       </c>
       <c r="E685" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F685" s="2">
         <v>28.5</v>
@@ -50525,7 +50528,7 @@
         <v>268</v>
       </c>
       <c r="E686" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F686" s="2">
         <v>28.5</v>
@@ -50551,7 +50554,7 @@
         <v>268</v>
       </c>
       <c r="E687" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F687" s="2">
         <v>28.5</v>
@@ -50577,7 +50580,7 @@
         <v>268</v>
       </c>
       <c r="E688" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F688" s="2">
         <v>52.250000000000007</v>
@@ -50603,7 +50606,7 @@
         <v>268</v>
       </c>
       <c r="E689" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F689" s="2">
         <v>76</v>
@@ -50629,7 +50632,7 @@
         <v>268</v>
       </c>
       <c r="E690" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F690" s="2">
         <v>61.75</v>
@@ -50655,7 +50658,7 @@
         <v>268</v>
       </c>
       <c r="E691" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F691" s="2">
         <v>52.250000000000007</v>
@@ -50681,7 +50684,7 @@
         <v>268</v>
       </c>
       <c r="E692" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F692" s="2">
         <v>38</v>
@@ -50707,7 +50710,7 @@
         <v>268</v>
       </c>
       <c r="E693" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F693" s="2">
         <v>76</v>
@@ -51019,7 +51022,7 @@
         <v>29</v>
       </c>
       <c r="E705" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F705" s="2">
         <v>128.93099122207073</v>
@@ -51045,7 +51048,7 @@
         <v>29</v>
       </c>
       <c r="E706" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F706" s="2">
         <v>58.538346457578221</v>
@@ -51097,7 +51100,7 @@
         <v>29</v>
       </c>
       <c r="E708" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F708" s="2">
         <v>493.2478219824888</v>
@@ -51149,7 +51152,7 @@
         <v>268</v>
       </c>
       <c r="E710" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F710" s="2">
         <v>280</v>
@@ -51175,7 +51178,7 @@
         <v>268</v>
       </c>
       <c r="E711" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F711" s="2">
         <v>95</v>
@@ -51201,7 +51204,7 @@
         <v>268</v>
       </c>
       <c r="E712" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F712" s="2">
         <v>55.000000000000007</v>
@@ -51227,7 +51230,7 @@
         <v>268</v>
       </c>
       <c r="E713" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F713" s="2">
         <v>220.00000000000003</v>
@@ -51253,7 +51256,7 @@
         <v>268</v>
       </c>
       <c r="E714" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F714" s="2">
         <v>80</v>
@@ -51279,7 +51282,7 @@
         <v>268</v>
       </c>
       <c r="E715" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F715" s="2">
         <v>50</v>
@@ -51305,7 +51308,7 @@
         <v>268</v>
       </c>
       <c r="E716" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F716" s="2">
         <v>229.99999999999997</v>
@@ -51331,7 +51334,7 @@
         <v>268</v>
       </c>
       <c r="E717" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F717" s="2">
         <v>80</v>
@@ -51357,7 +51360,7 @@
         <v>268</v>
       </c>
       <c r="E718" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F718" s="2">
         <v>45</v>
@@ -51383,7 +51386,7 @@
         <v>268</v>
       </c>
       <c r="E719" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F719" s="2">
         <v>150</v>
@@ -51409,7 +51412,7 @@
         <v>268</v>
       </c>
       <c r="E720" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F720" s="2">
         <v>90</v>
@@ -51435,7 +51438,7 @@
         <v>268</v>
       </c>
       <c r="E721" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F721" s="2">
         <v>185</v>
@@ -51461,7 +51464,7 @@
         <v>268</v>
       </c>
       <c r="E722" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F722" s="2">
         <v>75</v>
@@ -51487,7 +51490,7 @@
         <v>268</v>
       </c>
       <c r="E723" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F723" s="2">
         <v>70</v>
@@ -51513,7 +51516,7 @@
         <v>268</v>
       </c>
       <c r="E724" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F724" s="2">
         <v>70</v>
@@ -51539,7 +51542,7 @@
         <v>268</v>
       </c>
       <c r="E725" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F725" s="2">
         <v>30</v>
@@ -51565,7 +51568,7 @@
         <v>268</v>
       </c>
       <c r="E726" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F726" s="2">
         <v>65</v>
@@ -51591,7 +51594,7 @@
         <v>268</v>
       </c>
       <c r="E727" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F727" s="2">
         <v>35</v>
@@ -51617,7 +51620,7 @@
         <v>268</v>
       </c>
       <c r="E728" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F728" s="2">
         <v>80</v>
@@ -51643,7 +51646,7 @@
         <v>268</v>
       </c>
       <c r="E729" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F729" s="2">
         <v>170</v>
@@ -51669,7 +51672,7 @@
         <v>268</v>
       </c>
       <c r="E730" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F730" s="2">
         <v>80</v>
@@ -51695,7 +51698,7 @@
         <v>268</v>
       </c>
       <c r="E731" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F731" s="2">
         <v>170</v>
@@ -51721,7 +51724,7 @@
         <v>268</v>
       </c>
       <c r="E732" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F732" s="2">
         <v>80</v>
@@ -51747,7 +51750,7 @@
         <v>268</v>
       </c>
       <c r="E733" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F733" s="2">
         <v>225</v>
@@ -51773,7 +51776,7 @@
         <v>268</v>
       </c>
       <c r="E734" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F734" s="2">
         <v>35</v>
@@ -51799,7 +51802,7 @@
         <v>268</v>
       </c>
       <c r="E735" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F735" s="2">
         <v>120</v>
@@ -51825,7 +51828,7 @@
         <v>268</v>
       </c>
       <c r="E736" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F736" s="2">
         <v>75</v>
@@ -51851,7 +51854,7 @@
         <v>268</v>
       </c>
       <c r="E737" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F737" s="2">
         <v>30</v>
@@ -51877,7 +51880,7 @@
         <v>268</v>
       </c>
       <c r="E738" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F738" s="2">
         <v>55.000000000000007</v>
@@ -51903,7 +51906,7 @@
         <v>268</v>
       </c>
       <c r="E739" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F739" s="2">
         <v>55.000000000000007</v>
@@ -51929,7 +51932,7 @@
         <v>268</v>
       </c>
       <c r="E740" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F740" s="2">
         <v>55.000000000000007</v>
@@ -51955,7 +51958,7 @@
         <v>268</v>
       </c>
       <c r="E741" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F741" s="2">
         <v>85</v>
@@ -51981,7 +51984,7 @@
         <v>268</v>
       </c>
       <c r="E742" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F742" s="2">
         <v>25</v>
@@ -52007,7 +52010,7 @@
         <v>268</v>
       </c>
       <c r="E743" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F743" s="2">
         <v>185</v>
@@ -52033,7 +52036,7 @@
         <v>268</v>
       </c>
       <c r="E744" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F744" s="2">
         <v>55.000000000000007</v>
@@ -52059,7 +52062,7 @@
         <v>268</v>
       </c>
       <c r="E745" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F745" s="2">
         <v>110.00000000000001</v>
@@ -52085,7 +52088,7 @@
         <v>268</v>
       </c>
       <c r="E746" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F746" s="2">
         <v>35</v>
@@ -52111,7 +52114,7 @@
         <v>268</v>
       </c>
       <c r="E747" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F747" s="2">
         <v>114.99999999999999</v>
@@ -52137,7 +52140,7 @@
         <v>268</v>
       </c>
       <c r="E748" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F748" s="2">
         <v>40</v>
@@ -52163,7 +52166,7 @@
         <v>268</v>
       </c>
       <c r="E749" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F749" s="2">
         <v>195</v>
@@ -52189,7 +52192,7 @@
         <v>268</v>
       </c>
       <c r="E750" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F750" s="2">
         <v>195</v>
@@ -52215,7 +52218,7 @@
         <v>268</v>
       </c>
       <c r="E751" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F751" s="2">
         <v>195</v>
@@ -52241,7 +52244,7 @@
         <v>268</v>
       </c>
       <c r="E752" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F752" s="2">
         <v>90</v>
@@ -52267,7 +52270,7 @@
         <v>268</v>
       </c>
       <c r="E753" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F753" s="2">
         <v>55.000000000000007</v>
@@ -52293,7 +52296,7 @@
         <v>29</v>
       </c>
       <c r="E754" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F754" s="2">
         <v>127.71474392692691</v>
@@ -52319,7 +52322,7 @@
         <v>29</v>
       </c>
       <c r="E755" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F755" s="2">
         <v>119.28179284910652</v>
@@ -52345,7 +52348,7 @@
         <v>268</v>
       </c>
       <c r="E756" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F756" s="2">
         <v>78.569999999999993</v>
@@ -52371,7 +52374,7 @@
         <v>268</v>
       </c>
       <c r="E757" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F757" s="2">
         <v>78.569999999999993</v>
@@ -52397,7 +52400,7 @@
         <v>268</v>
       </c>
       <c r="E758" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F758" s="2">
         <v>78.569999999999993</v>
@@ -52449,7 +52452,7 @@
         <v>29</v>
       </c>
       <c r="E760" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F760" s="2">
         <v>104.04622665208515</v>
@@ -52475,7 +52478,7 @@
         <v>29</v>
       </c>
       <c r="E761" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F761" s="2">
         <v>79.06156217484407</v>
@@ -52605,7 +52608,7 @@
         <v>29</v>
       </c>
       <c r="E766" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F766" s="2">
         <v>127.98</v>
@@ -52683,7 +52686,7 @@
         <v>29</v>
       </c>
       <c r="E769" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F769" s="2">
         <v>123.5</v>
@@ -52891,7 +52894,7 @@
         <v>268</v>
       </c>
       <c r="E777" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F777" s="2">
         <v>162.46123</v>
@@ -52917,7 +52920,7 @@
         <v>268</v>
       </c>
       <c r="E778" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F778" s="2">
         <v>162.46123</v>
@@ -52943,7 +52946,7 @@
         <v>268</v>
       </c>
       <c r="E779" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F779" s="2">
         <v>162.46123</v>
@@ -52969,7 +52972,7 @@
         <v>268</v>
       </c>
       <c r="E780" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F780" s="2">
         <v>135.38435999999999</v>
@@ -52995,7 +52998,7 @@
         <v>268</v>
       </c>
       <c r="E781" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F781" s="2">
         <v>135.38435999999999</v>
@@ -53021,7 +53024,7 @@
         <v>268</v>
       </c>
       <c r="E782" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F782" s="2">
         <v>162.46123</v>
@@ -53047,7 +53050,7 @@
         <v>268</v>
       </c>
       <c r="E783" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F783" s="2">
         <v>135.38435000000001</v>
@@ -53073,7 +53076,7 @@
         <v>268</v>
       </c>
       <c r="E784" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F784" s="2">
         <v>67.692179999999993</v>
@@ -53099,7 +53102,7 @@
         <v>268</v>
       </c>
       <c r="E785" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F785" s="2">
         <v>67.692179999999993</v>
@@ -53125,7 +53128,7 @@
         <v>268</v>
       </c>
       <c r="E786" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F786" s="2">
         <v>67.692179999999993</v>
@@ -53151,7 +53154,7 @@
         <v>268</v>
       </c>
       <c r="E787" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F787" s="2">
         <v>67.692179999999993</v>
@@ -53229,7 +53232,7 @@
         <v>268</v>
       </c>
       <c r="E790" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F790" s="2">
         <v>150.76767000000001</v>
@@ -53255,7 +53258,7 @@
         <v>268</v>
       </c>
       <c r="E791" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F791" s="2">
         <v>150.76767000000001</v>
@@ -53281,7 +53284,7 @@
         <v>268</v>
       </c>
       <c r="E792" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F792" s="2">
         <v>150.76767000000001</v>
@@ -53307,7 +53310,7 @@
         <v>268</v>
       </c>
       <c r="E793" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F793" s="2">
         <v>150.76767000000001</v>
@@ -53333,7 +53336,7 @@
         <v>268</v>
       </c>
       <c r="E794" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F794" s="2">
         <v>54.37041</v>
@@ -53359,7 +53362,7 @@
         <v>268</v>
       </c>
       <c r="E795" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F795" s="2">
         <v>54.37041</v>
@@ -53385,7 +53388,7 @@
         <v>268</v>
       </c>
       <c r="E796" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F796" s="2">
         <v>60.51144</v>
@@ -53411,7 +53414,7 @@
         <v>268</v>
       </c>
       <c r="E797" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F797" s="2">
         <v>69.537059999999997</v>
@@ -53437,7 +53440,7 @@
         <v>268</v>
       </c>
       <c r="E798" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F798" s="2">
         <v>69.537059999999997</v>
@@ -54243,6 +54246,7 @@
       <c r="H1008" s="44"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H801" xr:uid="{8FC78394-D4E8-4F19-88C9-98DAC0E56E9A}"/>
   <conditionalFormatting sqref="A1 A962:A1048576">
     <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
